--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260827.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260827.xlsx
@@ -611,56 +611,56 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>132,835</t>
+          <t>133,185</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.14%</t>
+          <t>26.88%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>15,125</t>
+          <t>96,680</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.98%</t>
+          <t>7.97%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>96,380</t>
+          <t>15,225</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.94%</t>
+          <t>7.88%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>48,975</t>
+          <t>49,125</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.65%</t>
+          <t>6.44%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>116,895</t>
+          <t>117,145</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>57,390</t>
+          <t>57,540</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>4.32%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -770,24 +770,24 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,115</t>
+          <t>17,713</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -799,44 +799,44 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>43,555</t>
+          <t>19,115</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.93%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>17,713</t>
+          <t>43,555</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>74,115</t>
+          <t>74,415</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>57,138</t>
+          <t>57,288</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1041,44 +1041,44 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>75,413,159</t>
+          <t>7,690</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,690</t>
+          <t>9,236</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1117,56 +1117,56 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>122,235</t>
+          <t>122,385</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>9,236</t>
+          <t>17,745</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,745</t>
+          <t>57,488,699</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>611,255</t>
+          <t>720,169</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>108,914</t>
+          <t>-73,912</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
